--- a/output/tables/summary_table.xlsx
+++ b/output/tables/summary_table.xlsx
@@ -51,12 +51,6 @@
     <t>claim_over_value</t>
   </si>
   <si>
-    <t>claim_to_value_fl</t>
-  </si>
-  <si>
-    <t>claim_over_value_fl</t>
-  </si>
-  <si>
     <t>rl</t>
   </si>
   <si>
@@ -66,31 +60,37 @@
     <t>attom_matched</t>
   </si>
   <si>
-    <t>attom_value</t>
-  </si>
-  <si>
     <t>attom_value_2023</t>
   </si>
   <si>
+    <t>elevation</t>
+  </si>
+  <si>
+    <t>elevated</t>
+  </si>
+  <si>
     <t>builty_elevated</t>
   </si>
   <si>
     <t>builty_retrofit</t>
   </si>
   <si>
-    <t>builty_new_construction</t>
-  </si>
-  <si>
     <t>builty_elevation_year</t>
   </si>
   <si>
+    <t>builty_project_value</t>
+  </si>
+  <si>
+    <t>hma_p_fma</t>
+  </si>
+  <si>
+    <t>hma_p_hmgp</t>
+  </si>
+  <si>
     <t>fma_n_properties</t>
   </si>
   <si>
     <t>fma_spend</t>
-  </si>
-  <si>
-    <t>builty_project_value</t>
   </si>
   <si>
     <t>N_properties</t>
@@ -166,10 +166,10 @@
       </c>
       <c r="B2"/>
       <c r="C2">
-        <v>2014.2958491022455</v>
+        <v>2014.2771767909826</v>
       </c>
       <c r="D2">
-        <v>0.0020311198920160297</v>
+        <v>0.0020397924056821011</v>
       </c>
     </row>
     <row r="3">
@@ -178,10 +178,10 @@
       </c>
       <c r="B3"/>
       <c r="C3">
-        <v>4.8185170022361099</v>
+        <v>4.8188400578629871</v>
       </c>
       <c r="D3">
-        <v>0.0016794106806894212</v>
+        <v>0.00168842796630787</v>
       </c>
     </row>
     <row r="4">
@@ -189,13 +189,13 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>6101332</v>
+        <v>6053966</v>
       </c>
       <c r="C4">
-        <v>0.47247748524420569</v>
+        <v>0.47009811419489306</v>
       </c>
       <c r="D4">
-        <v>0.00020211510239017539</v>
+        <v>0.00020284860908512372</v>
       </c>
     </row>
     <row r="5">
@@ -204,10 +204,10 @@
       </c>
       <c r="B5"/>
       <c r="C5">
-        <v>0.58865526606822927</v>
+        <v>0.59073795790167061</v>
       </c>
       <c r="D5">
-        <v>0.00019920912897497284</v>
+        <v>0.00019983252120180794</v>
       </c>
     </row>
     <row r="6">
@@ -216,10 +216,10 @@
       </c>
       <c r="B6"/>
       <c r="C6">
-        <v>0.84749268560662427</v>
+        <v>0.84953624711816489</v>
       </c>
       <c r="D6">
-        <v>0.00014554224340180443</v>
+        <v>0.00014530310580628463</v>
       </c>
     </row>
     <row r="7">
@@ -227,13 +227,13 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>6101508</v>
+        <v>6054144</v>
       </c>
       <c r="C7">
-        <v>709.43469777147277</v>
+        <v>704.69627784344675</v>
       </c>
       <c r="D7">
-        <v>0.30408283445534801</v>
+        <v>0.30246181896854629</v>
       </c>
     </row>
     <row r="8">
@@ -241,13 +241,13 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>6101303</v>
+        <v>6053940</v>
       </c>
       <c r="C8">
-        <v>778.89200199250388</v>
+        <v>774.35752084946455</v>
       </c>
       <c r="D8">
-        <v>0.3395689943419305</v>
+        <v>0.33795515665774495</v>
       </c>
     </row>
     <row r="9">
@@ -256,10 +256,10 @@
       </c>
       <c r="B9"/>
       <c r="C9">
-        <v>0.036843040296522196</v>
+        <v>0.035995065987788517</v>
       </c>
       <c r="D9">
-        <v>7.6260915220895765e-05</v>
+        <v>7.5705792656604112e-05</v>
       </c>
     </row>
     <row r="10">
@@ -268,10 +268,10 @@
       </c>
       <c r="B10"/>
       <c r="C10">
-        <v>3962.6778016113808</v>
+        <v>3943.1763941153213</v>
       </c>
       <c r="D10">
-        <v>12.214540457496192</v>
+        <v>12.272558733832899</v>
       </c>
     </row>
     <row r="11">
@@ -279,13 +279,13 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>224804</v>
+        <v>217925</v>
       </c>
       <c r="C11">
-        <v>107555.6677657093</v>
+        <v>109547.69177122945</v>
       </c>
       <c r="D11">
-        <v>245.65945774914823</v>
+        <v>251.32073762112705</v>
       </c>
     </row>
     <row r="12">
@@ -293,13 +293,13 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>176027</v>
+        <v>128761</v>
       </c>
       <c r="C12">
-        <v>2.2277310218070019</v>
+        <v>0.53188854127459662</v>
       </c>
       <c r="D12">
-        <v>0.62862425556587731</v>
+        <v>0.0029952139075027965</v>
       </c>
     </row>
     <row r="13">
@@ -307,41 +307,37 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>176027</v>
+        <v>128761</v>
       </c>
       <c r="C13">
-        <v>0.26745328841598165</v>
+        <v>0.13129752021186539</v>
       </c>
       <c r="D13">
-        <v>0.0010550018531322494</v>
+        <v>0.00094118134061492974</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
         <v>12</v>
       </c>
-      <c r="B14">
-        <v>174951</v>
-      </c>
+      <c r="B14"/>
       <c r="C14">
-        <v>0.88438994780909241</v>
+        <v>0.0085200573080100733</v>
       </c>
       <c r="D14">
-        <v>0.0042678116676971196</v>
+        <v>3.7353493021301234e-05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
         <v>13</v>
       </c>
-      <c r="B15">
-        <v>174951</v>
-      </c>
+      <c r="B15"/>
       <c r="C15">
-        <v>0.26346234088401893</v>
+        <v>0.0015030634414999449</v>
       </c>
       <c r="D15">
-        <v>0.0010531731495250125</v>
+        <v>1.5744541566890485e-05</v>
       </c>
     </row>
     <row r="16">
@@ -350,22 +346,24 @@
       </c>
       <c r="B16"/>
       <c r="C16">
-        <v>0.0088765891556210532</v>
+        <v>0.84221533712721963</v>
       </c>
       <c r="D16">
-        <v>3.7971930373712492e-05</v>
+        <v>0.00014815351564034527</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
         <v>15</v>
       </c>
-      <c r="B17"/>
+      <c r="B17">
+        <v>3853165</v>
+      </c>
       <c r="C17">
-        <v>0.0016031681828640955</v>
+        <v>380746.76686287188</v>
       </c>
       <c r="D17">
-        <v>1.6196340129044625e-05</v>
+        <v>397.06383054847373</v>
       </c>
     </row>
     <row r="18">
@@ -374,24 +372,22 @@
       </c>
       <c r="B18"/>
       <c r="C18">
-        <v>0.84343412325941036</v>
+        <v>0.0012194634492960542</v>
       </c>
       <c r="D18">
-        <v>0.00014711260634526864</v>
+        <v>1.4183631019589879e-05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
         <v>17</v>
       </c>
-      <c r="B19">
-        <v>4928827</v>
-      </c>
+      <c r="B19"/>
       <c r="C19">
-        <v>269520.62379223295</v>
+        <v>0.066947106371634577</v>
       </c>
       <c r="D19">
-        <v>271.66401647024196</v>
+        <v>0.00010157504720155545</v>
       </c>
     </row>
     <row r="20">
@@ -399,13 +395,13 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>3897608</v>
+        <v>5099026</v>
       </c>
       <c r="C20">
-        <v>381272.1228542297</v>
+        <v>0.00078583635384483228</v>
       </c>
       <c r="D20">
-        <v>393.77825217301108</v>
+        <v>1.2409428413749977e-05</v>
       </c>
     </row>
     <row r="21">
@@ -413,13 +409,13 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>5146355</v>
+        <v>4007</v>
       </c>
       <c r="C21">
-        <v>0.00071778958116958504</v>
+        <v>0.86997753930621413</v>
       </c>
       <c r="D21">
-        <v>1.1805729409102474e-05</v>
+        <v>0.0053138310005471697</v>
       </c>
     </row>
     <row r="22">
@@ -427,13 +423,13 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>3694</v>
+        <v>4006</v>
       </c>
       <c r="C22">
-        <v>0.87087168381158631</v>
+        <v>2018.5464303544684</v>
       </c>
       <c r="D22">
-        <v>0.0055182093793244291</v>
+        <v>0.098024165153923537</v>
       </c>
     </row>
     <row r="23">
@@ -441,27 +437,25 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>3694</v>
+        <v>839</v>
       </c>
       <c r="C23">
-        <v>0.13183540877097996</v>
+        <v>167828.80223141148</v>
       </c>
       <c r="D23">
-        <v>0.0055670794025935748</v>
+        <v>11063.155434213153</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
         <v>22</v>
       </c>
-      <c r="B24">
-        <v>3694</v>
-      </c>
+      <c r="B24"/>
       <c r="C24">
-        <v>2018.6418516513265</v>
+        <v>0.00042685224903654765</v>
       </c>
       <c r="D24">
-        <v>0.099546598762882438</v>
+        <v>4.4459893349035954e-07</v>
       </c>
     </row>
     <row r="25">
@@ -470,10 +464,10 @@
       </c>
       <c r="B25"/>
       <c r="C25">
-        <v>115.78887641871043</v>
+        <v>0.00047584866096977296</v>
       </c>
       <c r="D25">
-        <v>0.094194554679845707</v>
+        <v>6.5914429579035355e-07</v>
       </c>
     </row>
     <row r="26">
@@ -482,24 +476,22 @@
       </c>
       <c r="B26"/>
       <c r="C26">
-        <v>27124596.276788663</v>
+        <v>116.02438563520617</v>
       </c>
       <c r="D26">
-        <v>19554.40889264147</v>
+        <v>0.094892790317051265</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
         <v>25</v>
       </c>
-      <c r="B27">
-        <v>1700</v>
-      </c>
+      <c r="B27"/>
       <c r="C27">
-        <v>297561.14322523004</v>
+        <v>27263504.397976574</v>
       </c>
       <c r="D27">
-        <v>15097.40656951219</v>
+        <v>19694.90430038366</v>
       </c>
     </row>
     <row r="28">
@@ -507,7 +499,7 @@
         <v>26</v>
       </c>
       <c r="B28">
-        <v>6101668</v>
+        <v>6054302</v>
       </c>
       <c r="C28"/>
       <c r="D28"/>

--- a/output/tables/summary_table.xlsx
+++ b/output/tables/summary_table.xlsx
@@ -13,96 +13,75 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="30" uniqueCount="30">
-  <si>
-    <t>policy_year_first</t>
-  </si>
-  <si>
-    <t>policy_years</t>
-  </si>
-  <si>
-    <t>sfha</t>
-  </si>
-  <si>
-    <t>post_firm</t>
-  </si>
-  <si>
-    <t>primary_residence</t>
-  </si>
-  <si>
-    <t>premium_first</t>
-  </si>
-  <si>
-    <t>premium_last</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="23" uniqueCount="23">
+  <si>
+    <t>premium_mean</t>
+  </si>
+  <si>
+    <t>premium_median</t>
+  </si>
+  <si>
+    <t>loss_ratio</t>
+  </si>
+  <si>
+    <t>n_property_years</t>
   </si>
   <si>
     <t>any_claim</t>
   </si>
   <si>
-    <t>claim_cb</t>
-  </si>
-  <si>
-    <t>claim_cb_claimant</t>
-  </si>
-  <si>
-    <t>claim_to_value</t>
-  </si>
-  <si>
-    <t>claim_over_value</t>
-  </si>
-  <si>
     <t>rl</t>
   </si>
   <si>
     <t>srl</t>
   </si>
   <si>
-    <t>attom_matched</t>
-  </si>
-  <si>
-    <t>attom_value_2023</t>
-  </si>
-  <si>
-    <t>elevation</t>
-  </si>
-  <si>
-    <t>elevated</t>
-  </si>
-  <si>
-    <t>builty_elevated</t>
-  </si>
-  <si>
-    <t>builty_retrofit</t>
-  </si>
-  <si>
-    <t>builty_elevation_year</t>
-  </si>
-  <si>
-    <t>builty_project_value</t>
-  </si>
-  <si>
-    <t>hma_p_fma</t>
-  </si>
-  <si>
-    <t>hma_p_hmgp</t>
-  </si>
-  <si>
-    <t>fma_n_properties</t>
-  </si>
-  <si>
-    <t>fma_spend</t>
-  </si>
-  <si>
-    <t>N_properties</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>mean</t>
-  </si>
-  <si>
-    <t>se</t>
+    <t>claim_claimants_mean</t>
+  </si>
+  <si>
+    <t>claim_claimants_median</t>
+  </si>
+  <si>
+    <t>claim_rl_median</t>
+  </si>
+  <si>
+    <t>claim_srl_median</t>
+  </si>
+  <si>
+    <t>elevated_first</t>
+  </si>
+  <si>
+    <t>elevation_any</t>
+  </si>
+  <si>
+    <t>elevation_nfip</t>
+  </si>
+  <si>
+    <t>elevation_builty</t>
+  </si>
+  <si>
+    <t>grant_funded_share</t>
+  </si>
+  <si>
+    <t>retrofit_cost_mean</t>
+  </si>
+  <si>
+    <t>retrofit_cost_median</t>
+  </si>
+  <si>
+    <t>retrofit_cost_n</t>
+  </si>
+  <si>
+    <t>n_properties</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Pre_FIRM</t>
+  </si>
+  <si>
+    <t>Post_FIRM</t>
   </si>
 </sst>
 </file>
@@ -146,42 +125,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2"/>
+      <c r="B2">
+        <v>740.41618841460627</v>
+      </c>
       <c r="C2">
-        <v>2014.2771767909826</v>
+        <v>962.67128207544852</v>
       </c>
       <c r="D2">
-        <v>0.0020397924056821011</v>
+        <v>607.68894441976738</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3"/>
+      <c r="B3">
+        <v>493.07278453366809</v>
+      </c>
       <c r="C3">
-        <v>4.8188400578629871</v>
+        <v>539.12903363846124</v>
       </c>
       <c r="D3">
-        <v>0.00168842796630787</v>
+        <v>472.459228515625</v>
       </c>
     </row>
     <row r="4">
@@ -189,37 +172,41 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>6053966</v>
+        <v>1.0954553921674419</v>
       </c>
       <c r="C4">
-        <v>0.47009811419489306</v>
+        <v>1.387154663409299</v>
       </c>
       <c r="D4">
-        <v>0.00020284860908512372</v>
+        <v>0.8194990505948887</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5"/>
+      <c r="B5">
+        <v>29.174713000000001</v>
+      </c>
       <c r="C5">
-        <v>0.59073795790167061</v>
+        <v>10.908306</v>
       </c>
       <c r="D5">
-        <v>0.00019983252120180794</v>
+        <v>18.266407000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6"/>
+      <c r="B6">
+        <v>0.035995065987788497</v>
+      </c>
       <c r="C6">
-        <v>0.84953624711816489</v>
+        <v>0.0515268407891529</v>
       </c>
       <c r="D6">
-        <v>0.00014530310580628463</v>
+        <v>0.025234684353947701</v>
       </c>
     </row>
     <row r="7">
@@ -227,13 +214,13 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>6054144</v>
+        <v>0.0085200573080100993</v>
       </c>
       <c r="C7">
-        <v>704.69627784344675</v>
+        <v>0.014857962479558401</v>
       </c>
       <c r="D7">
-        <v>0.30246181896854629</v>
+        <v>0.0041291696421031999</v>
       </c>
     </row>
     <row r="8">
@@ -241,37 +228,41 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>6053940</v>
+        <v>0.0015030634414999</v>
       </c>
       <c r="C8">
-        <v>774.35752084946455</v>
+        <v>0.0031229366743671001</v>
       </c>
       <c r="D8">
-        <v>0.33795515665774495</v>
+        <v>0.00038081859781590003</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>7</v>
       </c>
-      <c r="B9"/>
+      <c r="B9">
+        <v>109.54769177122949</v>
+      </c>
       <c r="C9">
-        <v>0.035995065987788517</v>
+        <v>115.44148318459069</v>
       </c>
       <c r="D9">
-        <v>7.5705792656604112e-05</v>
+        <v>101.2101698202692</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B10"/>
+      <c r="B10">
+        <v>82.334812499999998</v>
+      </c>
       <c r="C10">
-        <v>3943.1763941153213</v>
+        <v>92.797515625000003</v>
       </c>
       <c r="D10">
-        <v>12.272558733832899</v>
+        <v>59.983904296874996</v>
       </c>
     </row>
     <row r="11">
@@ -279,13 +270,13 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>217925</v>
+        <v>101.59911328125</v>
       </c>
       <c r="C11">
-        <v>109547.69177122945</v>
+        <v>108.25746875</v>
       </c>
       <c r="D11">
-        <v>251.32073762112705</v>
+        <v>81.810140625000003</v>
       </c>
     </row>
     <row r="12">
@@ -293,13 +284,13 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>128761</v>
+        <v>127.2714296875</v>
       </c>
       <c r="C12">
-        <v>0.53188854127459662</v>
+        <v>130.31388671875001</v>
       </c>
       <c r="D12">
-        <v>0.0029952139075027965</v>
+        <v>109.98459375</v>
       </c>
     </row>
     <row r="13">
@@ -307,49 +298,55 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>128761</v>
+        <v>403939</v>
       </c>
       <c r="C13">
-        <v>0.13129752021186539</v>
+        <v>155079</v>
       </c>
       <c r="D13">
-        <v>0.00094118134061492974</v>
+        <v>248860</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
         <v>12</v>
       </c>
-      <c r="B14"/>
+      <c r="B14">
+        <v>7383</v>
+      </c>
       <c r="C14">
-        <v>0.0085200573080100733</v>
+        <v>5186</v>
       </c>
       <c r="D14">
-        <v>3.7353493021301234e-05</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
         <v>13</v>
       </c>
-      <c r="B15"/>
+      <c r="B15">
+        <v>3928</v>
+      </c>
       <c r="C15">
-        <v>0.0015030634414999449</v>
+        <v>2816</v>
       </c>
       <c r="D15">
-        <v>1.5744541566890485e-05</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
         <v>14</v>
       </c>
-      <c r="B16"/>
+      <c r="B16">
+        <v>3486</v>
+      </c>
       <c r="C16">
-        <v>0.84221533712721963</v>
+        <v>2394</v>
       </c>
       <c r="D16">
-        <v>0.00014815351564034527</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="17">
@@ -357,37 +354,41 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>3853165</v>
+        <v>0.015490533562822701</v>
       </c>
       <c r="C17">
-        <v>380746.76686287188</v>
+        <v>0.0154553049289891</v>
       </c>
       <c r="D17">
-        <v>397.06383054847373</v>
+        <v>0.015567765567765599</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
         <v>16</v>
       </c>
-      <c r="B18"/>
+      <c r="B18">
+        <v>167.82880223141149</v>
+      </c>
       <c r="C18">
-        <v>0.0012194634492960542</v>
+        <v>186.41837525027159</v>
       </c>
       <c r="D18">
-        <v>1.4183631019589879e-05</v>
+        <v>113.1946580539166</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
         <v>17</v>
       </c>
-      <c r="B19"/>
+      <c r="B19">
+        <v>67.023136551601482</v>
+      </c>
       <c r="C19">
-        <v>0.066947106371634577</v>
+        <v>93.707744457925131</v>
       </c>
       <c r="D19">
-        <v>0.00010157504720155545</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
@@ -395,13 +396,13 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>5099026</v>
+        <v>839</v>
       </c>
       <c r="C20">
-        <v>0.00078583635384483228</v>
+        <v>626</v>
       </c>
       <c r="D20">
-        <v>1.2409428413749977e-05</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21">
@@ -409,100 +410,14 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>4007</v>
+        <v>6.0543019999999999</v>
       </c>
       <c r="C21">
-        <v>0.86997753930621413</v>
+        <v>2.4777960000000001</v>
       </c>
       <c r="D21">
-        <v>0.0053138310005471697</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22">
-        <v>4006</v>
-      </c>
-      <c r="C22">
-        <v>2018.5464303544684</v>
-      </c>
-      <c r="D22">
-        <v>0.098024165153923537</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23">
-        <v>839</v>
-      </c>
-      <c r="C23">
-        <v>167828.80223141148</v>
-      </c>
-      <c r="D23">
-        <v>11063.155434213153</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24"/>
-      <c r="C24">
-        <v>0.00042685224903654765</v>
-      </c>
-      <c r="D24">
-        <v>4.4459893349035954e-07</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25"/>
-      <c r="C25">
-        <v>0.00047584866096977296</v>
-      </c>
-      <c r="D25">
-        <v>6.5914429579035355e-07</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26"/>
-      <c r="C26">
-        <v>116.02438563520617</v>
-      </c>
-      <c r="D26">
-        <v>0.094892790317051265</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27"/>
-      <c r="C27">
-        <v>27263504.397976574</v>
-      </c>
-      <c r="D27">
-        <v>19694.90430038366</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28">
-        <v>6054302</v>
-      </c>
-      <c r="C28"/>
-      <c r="D28"/>
+        <v>3.5765060000000002</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>

--- a/output/tables/summary_table.xlsx
+++ b/output/tables/summary_table.xlsx
@@ -13,75 +13,99 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="23" uniqueCount="23">
-  <si>
-    <t>premium_mean</t>
-  </si>
-  <si>
-    <t>premium_median</t>
-  </si>
-  <si>
-    <t>loss_ratio</t>
-  </si>
-  <si>
-    <t>n_property_years</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="31" uniqueCount="31">
+  <si>
+    <t>policy_year_first</t>
+  </si>
+  <si>
+    <t>policy_years</t>
+  </si>
+  <si>
+    <t>sfha</t>
+  </si>
+  <si>
+    <t>post_firm</t>
+  </si>
+  <si>
+    <t>primary_residence</t>
+  </si>
+  <si>
+    <t>premium_first</t>
+  </si>
+  <si>
+    <t>premium_last</t>
   </si>
   <si>
     <t>any_claim</t>
   </si>
   <si>
+    <t>claim_cb</t>
+  </si>
+  <si>
+    <t>claim_cb_claimant</t>
+  </si>
+  <si>
+    <t>claim_to_value</t>
+  </si>
+  <si>
+    <t>claim_over_value</t>
+  </si>
+  <si>
     <t>rl</t>
   </si>
   <si>
     <t>srl</t>
   </si>
   <si>
-    <t>claim_claimants_mean</t>
-  </si>
-  <si>
-    <t>claim_claimants_median</t>
-  </si>
-  <si>
-    <t>claim_rl_median</t>
-  </si>
-  <si>
-    <t>claim_srl_median</t>
-  </si>
-  <si>
-    <t>elevated_first</t>
-  </si>
-  <si>
-    <t>elevation_any</t>
-  </si>
-  <si>
-    <t>elevation_nfip</t>
-  </si>
-  <si>
-    <t>elevation_builty</t>
-  </si>
-  <si>
-    <t>grant_funded_share</t>
-  </si>
-  <si>
-    <t>retrofit_cost_mean</t>
-  </si>
-  <si>
-    <t>retrofit_cost_median</t>
-  </si>
-  <si>
-    <t>retrofit_cost_n</t>
-  </si>
-  <si>
-    <t>n_properties</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-  <si>
-    <t>Pre_FIRM</t>
-  </si>
-  <si>
-    <t>Post_FIRM</t>
+    <t>attom_matched</t>
+  </si>
+  <si>
+    <t>attom_value_2023</t>
+  </si>
+  <si>
+    <t>elevation</t>
+  </si>
+  <si>
+    <t>elevated</t>
+  </si>
+  <si>
+    <t>builty_elevated</t>
+  </si>
+  <si>
+    <t>builty_retrofit</t>
+  </si>
+  <si>
+    <t>builty_elevation_year</t>
+  </si>
+  <si>
+    <t>builty_project_value</t>
+  </si>
+  <si>
+    <t>hma_p_fma</t>
+  </si>
+  <si>
+    <t>hma_p_hmgp</t>
+  </si>
+  <si>
+    <t>fma_n_properties</t>
+  </si>
+  <si>
+    <t>fma_spend</t>
+  </si>
+  <si>
+    <t>N_properties</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>mean_all</t>
+  </si>
+  <si>
+    <t>mean_pre_firm</t>
+  </si>
+  <si>
+    <t>mean_post_firm</t>
   </si>
 </sst>
 </file>
@@ -125,46 +149,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s">
-        <v>22</v>
+        <v>29</v>
+      </c>
+      <c r="E1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>740.41618841460627</v>
-      </c>
+      <c r="B2"/>
       <c r="C2">
-        <v>962.67128207544852</v>
+        <v>2014.2771767909826</v>
       </c>
       <c r="D2">
-        <v>607.68894441976738</v>
+        <v>2015.6931220326451</v>
+      </c>
+      <c r="E2">
+        <v>2013.2962128401296</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3">
-        <v>493.07278453366809</v>
-      </c>
+      <c r="B3"/>
       <c r="C3">
-        <v>539.12903363846124</v>
+        <v>4.8188400578629871</v>
       </c>
       <c r="D3">
-        <v>472.459228515625</v>
+        <v>4.4357412797502294</v>
+      </c>
+      <c r="E3">
+        <v>5.0842501033131215</v>
       </c>
     </row>
     <row r="4">
@@ -172,41 +201,46 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>1.0954553921674419</v>
+        <v>6053966</v>
       </c>
       <c r="C4">
-        <v>1.387154663409299</v>
+        <v>0.47009811419489306</v>
       </c>
       <c r="D4">
-        <v>0.8194990505948887</v>
+        <v>0.55698411148036964</v>
+      </c>
+      <c r="E4">
+        <v>0.40990451658796395</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>29.174713000000001</v>
-      </c>
+      <c r="B5"/>
       <c r="C5">
-        <v>10.908306</v>
+        <v>0.59073795790167061</v>
       </c>
       <c r="D5">
-        <v>18.266407000000001</v>
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6">
-        <v>0.035995065987788497</v>
-      </c>
+      <c r="B6"/>
       <c r="C6">
-        <v>0.0515268407891529</v>
+        <v>0.84953624711816489</v>
       </c>
       <c r="D6">
-        <v>0.025234684353947701</v>
+        <v>0.82668226117081467</v>
+      </c>
+      <c r="E6">
+        <v>0.86536944157230544</v>
       </c>
     </row>
     <row r="7">
@@ -214,13 +248,16 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0.0085200573080100993</v>
+        <v>6054144</v>
       </c>
       <c r="C7">
-        <v>0.014857962479558401</v>
+        <v>704.69627784344675</v>
       </c>
       <c r="D7">
-        <v>0.0041291696421031999</v>
+        <v>903.94056462411049</v>
+      </c>
+      <c r="E7">
+        <v>566.65858001462675</v>
       </c>
     </row>
     <row r="8">
@@ -228,41 +265,46 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0.0015030634414999</v>
+        <v>6053940</v>
       </c>
       <c r="C8">
-        <v>0.0031229366743671001</v>
+        <v>774.35752084946455</v>
       </c>
       <c r="D8">
-        <v>0.00038081859781590003</v>
+        <v>997.14089504033393</v>
+      </c>
+      <c r="E8">
+        <v>620.01058321788901</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>7</v>
       </c>
-      <c r="B9">
-        <v>109.54769177122949</v>
-      </c>
+      <c r="B9"/>
       <c r="C9">
-        <v>115.44148318459069</v>
+        <v>0.035995065987788517</v>
       </c>
       <c r="D9">
-        <v>101.2101698202692</v>
+        <v>0.051526840789152942</v>
+      </c>
+      <c r="E9">
+        <v>0.02523468435394768</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B10">
-        <v>82.334812499999998</v>
-      </c>
+      <c r="B10"/>
       <c r="C10">
-        <v>92.797515625000003</v>
+        <v>3943.1763941153213</v>
       </c>
       <c r="D10">
-        <v>59.983904296874996</v>
+        <v>5948.3349245160798</v>
+      </c>
+      <c r="E10">
+        <v>2554.0066888239344</v>
       </c>
     </row>
     <row r="11">
@@ -270,13 +312,16 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>101.59911328125</v>
+        <v>217925</v>
       </c>
       <c r="C11">
-        <v>108.25746875</v>
+        <v>109547.69177122945</v>
       </c>
       <c r="D11">
-        <v>81.810140625000003</v>
+        <v>115441.48318459067</v>
+      </c>
+      <c r="E11">
+        <v>101210.16982026919</v>
       </c>
     </row>
     <row r="12">
@@ -284,13 +329,16 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>127.2714296875</v>
+        <v>118483</v>
       </c>
       <c r="C12">
-        <v>130.31388671875001</v>
+        <v>0.49459263205503046</v>
       </c>
       <c r="D12">
-        <v>109.98459375</v>
+        <v>0.56398772239589612</v>
+      </c>
+      <c r="E12">
+        <v>0.3959454879570809</v>
       </c>
     </row>
     <row r="13">
@@ -298,55 +346,61 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>403939</v>
+        <v>118483</v>
       </c>
       <c r="C13">
-        <v>155079</v>
+        <v>0.11808445093388925</v>
       </c>
       <c r="D13">
-        <v>248860</v>
+        <v>0.13567875319895334</v>
+      </c>
+      <c r="E13">
+        <v>0.093073637311206034</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
         <v>12</v>
       </c>
-      <c r="B14">
-        <v>7383</v>
-      </c>
+      <c r="B14"/>
       <c r="C14">
-        <v>5186</v>
+        <v>0.0085200573080100733</v>
       </c>
       <c r="D14">
-        <v>2197</v>
+        <v>0.014857962479558446</v>
+      </c>
+      <c r="E14">
+        <v>0.0041291696421032146</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
         <v>13</v>
       </c>
-      <c r="B15">
-        <v>3928</v>
-      </c>
+      <c r="B15"/>
       <c r="C15">
-        <v>2816</v>
+        <v>0.0015030634414999449</v>
       </c>
       <c r="D15">
-        <v>1112</v>
+        <v>0.0031229366743670585</v>
+      </c>
+      <c r="E15">
+        <v>0.00038081859781585715</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
         <v>14</v>
       </c>
-      <c r="B16">
-        <v>3486</v>
-      </c>
+      <c r="B16"/>
       <c r="C16">
-        <v>2394</v>
+        <v>0.84221533712721963</v>
       </c>
       <c r="D16">
-        <v>1092</v>
+        <v>0.84983307746077563</v>
+      </c>
+      <c r="E16">
+        <v>0.83693778229366877</v>
       </c>
     </row>
     <row r="17">
@@ -354,41 +408,46 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>0.015490533562822701</v>
+        <v>3641558</v>
       </c>
       <c r="C17">
-        <v>0.0154553049289891</v>
+        <v>390918.74748123932</v>
       </c>
       <c r="D17">
-        <v>0.015567765567765599</v>
+        <v>374229.45136791829</v>
+      </c>
+      <c r="E17">
+        <v>402086.60820066731</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
         <v>16</v>
       </c>
-      <c r="B18">
-        <v>167.82880223141149</v>
-      </c>
+      <c r="B18"/>
       <c r="C18">
-        <v>186.41837525027159</v>
+        <v>0.0012194634492960542</v>
       </c>
       <c r="D18">
-        <v>113.1946580539166</v>
+        <v>0.0020929890919187859</v>
+      </c>
+      <c r="E18">
+        <v>0.00061428668091148173</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
         <v>17</v>
       </c>
-      <c r="B19">
-        <v>67.023136551601482</v>
-      </c>
+      <c r="B19"/>
       <c r="C19">
-        <v>93.707744457925131</v>
+        <v>0.066947106371634577</v>
       </c>
       <c r="D19">
-        <v>30</v>
+        <v>0.062933348830977204</v>
+      </c>
+      <c r="E19">
+        <v>0.069727829339584504</v>
       </c>
     </row>
     <row r="20">
@@ -396,13 +455,16 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>839</v>
+        <v>5099026</v>
       </c>
       <c r="C20">
-        <v>626</v>
+        <v>0.00078583635384483228</v>
       </c>
       <c r="D20">
-        <v>213</v>
+        <v>0.001317843409809409</v>
+      </c>
+      <c r="E20">
+        <v>0.00041158408759792245</v>
       </c>
     </row>
     <row r="21">
@@ -410,13 +472,127 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>6.0543019999999999</v>
+        <v>4007</v>
       </c>
       <c r="C21">
-        <v>2.4777960000000001</v>
+        <v>0.86997753930621413</v>
       </c>
       <c r="D21">
-        <v>3.5765060000000002</v>
+        <v>0.86270270270270266</v>
+      </c>
+      <c r="E21">
+        <v>0.88636363636363635</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>4006</v>
+      </c>
+      <c r="C22">
+        <v>2018.5464303544684</v>
+      </c>
+      <c r="D22">
+        <v>2019.1524873828407</v>
+      </c>
+      <c r="E22">
+        <v>2017.1818181818182</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>804</v>
+      </c>
+      <c r="C23">
+        <v>151226.00800899879</v>
+      </c>
+      <c r="D23">
+        <v>166701.5778148926</v>
+      </c>
+      <c r="E23">
+        <v>106301.78109674389</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24"/>
+      <c r="C24">
+        <v>0.00042685224903654765</v>
+      </c>
+      <c r="D24">
+        <v>0.00046709506816034862</v>
+      </c>
+      <c r="E24">
+        <v>0.00039897210672623759</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25"/>
+      <c r="C25">
+        <v>0.00047584866096977296</v>
+      </c>
+      <c r="D25">
+        <v>0.00050432869268303329</v>
+      </c>
+      <c r="E25">
+        <v>0.00045611775358167143</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26"/>
+      <c r="C26">
+        <v>116.02438563520617</v>
+      </c>
+      <c r="D26">
+        <v>131.27925543507214</v>
+      </c>
+      <c r="E26">
+        <v>105.45584321681552</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27"/>
+      <c r="C27">
+        <v>27263504.397976574</v>
+      </c>
+      <c r="D27">
+        <v>29997416.656816632</v>
+      </c>
+      <c r="E27">
+        <v>25369455.608654019</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>6054302</v>
+      </c>
+      <c r="C28">
+        <v>6054302</v>
+      </c>
+      <c r="D28">
+        <v>2477796</v>
+      </c>
+      <c r="E28">
+        <v>3576506</v>
       </c>
     </row>
   </sheetData>
